--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>136555925</v>
       </c>
       <c r="B8" t="n">
-        <v>104489</v>
+        <v>104492</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136555855</v>
       </c>
       <c r="B10" t="n">
-        <v>98196</v>
+        <v>98199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>136555925</v>
       </c>
       <c r="B8" t="n">
-        <v>104492</v>
+        <v>104493</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136555855</v>
       </c>
       <c r="B10" t="n">
-        <v>98199</v>
+        <v>98200</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>136555925</v>
       </c>
       <c r="B8" t="n">
-        <v>104493</v>
+        <v>104498</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136555855</v>
       </c>
       <c r="B10" t="n">
-        <v>98200</v>
+        <v>98205</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>136555925</v>
       </c>
       <c r="B8" t="n">
-        <v>104498</v>
+        <v>104500</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136555855</v>
       </c>
       <c r="B10" t="n">
-        <v>98205</v>
+        <v>98207</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>136555925</v>
       </c>
       <c r="B8" t="n">
-        <v>104500</v>
+        <v>104506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136555855</v>
       </c>
       <c r="B10" t="n">
-        <v>98207</v>
+        <v>98213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>136555925</v>
       </c>
       <c r="B8" t="n">
-        <v>104506</v>
+        <v>104508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136555855</v>
       </c>
       <c r="B10" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>136555925</v>
       </c>
       <c r="B8" t="n">
-        <v>104508</v>
+        <v>104509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136555855</v>
       </c>
       <c r="B10" t="n">
-        <v>98215</v>
+        <v>98216</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>136555925</v>
       </c>
       <c r="B8" t="n">
-        <v>104509</v>
+        <v>104515</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136555855</v>
       </c>
       <c r="B10" t="n">
-        <v>98216</v>
+        <v>98222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>136555925</v>
       </c>
       <c r="B8" t="n">
-        <v>104515</v>
+        <v>104519</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136555855</v>
       </c>
       <c r="B10" t="n">
-        <v>98222</v>
+        <v>98226</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14042-2023 artfynd.xlsx
+++ b/artfynd/A 14042-2023 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>136555925</v>
       </c>
       <c r="B8" t="n">
-        <v>104519</v>
+        <v>104521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136555855</v>
       </c>
       <c r="B10" t="n">
-        <v>98226</v>
+        <v>98228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
